--- a/artfynd/A 12633-2025 artfynd.xlsx
+++ b/artfynd/A 12633-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124026250</v>
+        <v>124026065</v>
       </c>
       <c r="B2" t="n">
-        <v>96982</v>
+        <v>96985</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221946</v>
+        <v>221941</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -721,7 +721,7 @@
         <v>6621174</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124026065</v>
+        <v>124026250</v>
       </c>
       <c r="B3" t="n">
-        <v>96985</v>
+        <v>96982</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,16 +803,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>221946</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -833,7 +833,7 @@
         <v>6621174</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>

--- a/artfynd/A 12633-2025 artfynd.xlsx
+++ b/artfynd/A 12633-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -897,6 +897,233 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>124749055</v>
+      </c>
+      <c r="B4" t="n">
+        <v>95551</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>210</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Buxbaumia viridis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>utan kapsel</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Sundbergen V om Älvsbacka, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>423653</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6621145</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Älvsbacka</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Protonema (förgrodden) på en murken låga</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Carl A Andersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Carl A Andersson, Jonas Sjöblom</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>124749064</v>
+      </c>
+      <c r="B5" t="n">
+        <v>95455</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2818</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Stubbspretmossa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Sundbergen V om Älvsbacka, Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>423653</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6621145</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Älvsbacka</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Carl A Andersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Carl A Andersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 12633-2025 artfynd.xlsx
+++ b/artfynd/A 12633-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124026065</v>
+        <v>124026250</v>
       </c>
       <c r="B2" t="n">
-        <v>96985</v>
+        <v>96982</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221941</v>
+        <v>221946</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -721,7 +721,7 @@
         <v>6621174</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124026250</v>
+        <v>124026065</v>
       </c>
       <c r="B3" t="n">
-        <v>96982</v>
+        <v>96985</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,16 +803,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221946</v>
+        <v>221941</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -833,7 +833,7 @@
         <v>6621174</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124749055</v>
+        <v>124749064</v>
       </c>
       <c r="B4" t="n">
-        <v>95551</v>
+        <v>95455</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,28 +915,28 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>210</v>
+        <v>2818</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>utan kapsel</t>
+          <t>med kapsel</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
@@ -985,11 +985,6 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Protonema (förgrodden) på en murken låga</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1008,17 +1003,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Carl A Andersson, Jonas Sjöblom</t>
+          <t>Carl A Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124749064</v>
+        <v>124749055</v>
       </c>
       <c r="B5" t="n">
-        <v>95455</v>
+        <v>95551</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,28 +1026,28 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2818</v>
+        <v>210</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>med kapsel</t>
+          <t>utan kapsel</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
@@ -1101,6 +1096,11 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Protonema (förgrodden) på en murken låga</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1119,7 +1119,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Carl A Andersson</t>
+          <t>Carl A Andersson, Jonas Sjöblom</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 12633-2025 artfynd.xlsx
+++ b/artfynd/A 12633-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124026250</v>
+        <v>124026065</v>
       </c>
       <c r="B2" t="n">
-        <v>96982</v>
+        <v>96985</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221946</v>
+        <v>221941</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -721,7 +721,7 @@
         <v>6621174</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124026065</v>
+        <v>124026250</v>
       </c>
       <c r="B3" t="n">
-        <v>96985</v>
+        <v>96982</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,16 +803,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>221946</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -833,7 +833,7 @@
         <v>6621174</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124749064</v>
+        <v>124749055</v>
       </c>
       <c r="B4" t="n">
-        <v>95455</v>
+        <v>95551</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,28 +915,28 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2818</v>
+        <v>210</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>med kapsel</t>
+          <t>utan kapsel</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
@@ -985,6 +985,11 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Protonema (förgrodden) på en murken låga</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1003,17 +1008,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Carl A Andersson</t>
+          <t>Carl A Andersson, Jonas Sjöblom</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124749055</v>
+        <v>124749064</v>
       </c>
       <c r="B5" t="n">
-        <v>95551</v>
+        <v>95455</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1026,28 +1031,28 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>210</v>
+        <v>2818</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>utan kapsel</t>
+          <t>med kapsel</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
@@ -1096,11 +1101,6 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Protonema (förgrodden) på en murken låga</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1119,7 +1119,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Carl A Andersson, Jonas Sjöblom</t>
+          <t>Carl A Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 12633-2025 artfynd.xlsx
+++ b/artfynd/A 12633-2025 artfynd.xlsx
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124749055</v>
+        <v>124749064</v>
       </c>
       <c r="B4" t="n">
-        <v>95551</v>
+        <v>95455</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,28 +915,28 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>210</v>
+        <v>2818</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>utan kapsel</t>
+          <t>med kapsel</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
@@ -985,11 +985,6 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Protonema (förgrodden) på en murken låga</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1008,17 +1003,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Carl A Andersson, Jonas Sjöblom</t>
+          <t>Carl A Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124749064</v>
+        <v>124749055</v>
       </c>
       <c r="B5" t="n">
-        <v>95455</v>
+        <v>95551</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,28 +1026,28 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2818</v>
+        <v>210</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>med kapsel</t>
+          <t>utan kapsel</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
@@ -1101,6 +1096,11 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Protonema (förgrodden) på en murken låga</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1119,7 +1119,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Carl A Andersson</t>
+          <t>Carl A Andersson, Jonas Sjöblom</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 12633-2025 artfynd.xlsx
+++ b/artfynd/A 12633-2025 artfynd.xlsx
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124749064</v>
+        <v>124749055</v>
       </c>
       <c r="B4" t="n">
-        <v>95455</v>
+        <v>95551</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,28 +915,28 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2818</v>
+        <v>210</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>med kapsel</t>
+          <t>utan kapsel</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
@@ -985,6 +985,11 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Protonema (förgrodden) på en murken låga</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1003,17 +1008,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Carl A Andersson</t>
+          <t>Carl A Andersson, Jonas Sjöblom</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124749055</v>
+        <v>124749064</v>
       </c>
       <c r="B5" t="n">
-        <v>95551</v>
+        <v>95455</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1026,28 +1031,28 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>210</v>
+        <v>2818</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>utan kapsel</t>
+          <t>med kapsel</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
@@ -1096,11 +1101,6 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Protonema (förgrodden) på en murken låga</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1119,7 +1119,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Carl A Andersson, Jonas Sjöblom</t>
+          <t>Carl A Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 12633-2025 artfynd.xlsx
+++ b/artfynd/A 12633-2025 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>124749064</v>
       </c>
       <c r="B4" t="n">
-        <v>95455</v>
+        <v>95623</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>124749055</v>
       </c>
       <c r="B5" t="n">
-        <v>95551</v>
+        <v>95719</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 12633-2025 artfynd.xlsx
+++ b/artfynd/A 12633-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124026065</v>
+        <v>124749055</v>
       </c>
       <c r="B2" t="n">
-        <v>96985</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,45 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221941</v>
+        <v>210</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>utan kapsel</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tjuvtjärnen, Tjuvtjärnen, Vrm</t>
+          <t>Sundbergen V om Älvsbacka, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>423537</v>
+        <v>423653</v>
       </c>
       <c r="R2" t="n">
-        <v>6621174</v>
+        <v>6621145</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +748,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-04-13</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>10:34</t>
+          <t>2025-05-03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-04-13</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>10:34</t>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Protonema (förgrodden) på en murken låga</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,33 +767,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jonas Sjöblom</t>
+          <t>Carl A Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jonas Sjöblom</t>
+          <t>Carl A Andersson, Jonas Sjöblom</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124026250</v>
+        <v>124749064</v>
       </c>
       <c r="B3" t="n">
-        <v>96982</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96458</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,37 +797,45 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221946</v>
+        <v>2818</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tjuvtjärnen, Tjuvtjärnen, Vrm</t>
+          <t>Sundbergen V om Älvsbacka, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>423537</v>
+        <v>423653</v>
       </c>
       <c r="R3" t="n">
-        <v>6621174</v>
+        <v>6621145</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,22 +859,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-04-13</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>10:34</t>
+          <t>2025-05-03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-04-13</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>10:34</t>
+          <t>2025-05-03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,33 +873,29 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jonas Sjöblom</t>
+          <t>Carl A Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jonas Sjöblom</t>
+          <t>Carl A Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124749064</v>
+        <v>124026065</v>
       </c>
       <c r="B4" t="n">
-        <v>95623</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,45 +903,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2818</v>
+        <v>221941</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sundbergen V om Älvsbacka, Vrm</t>
+          <t>Tjuvtjärnen, Tjuvtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>423653</v>
+        <v>423537</v>
       </c>
       <c r="R4" t="n">
-        <v>6621145</v>
+        <v>6621174</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -977,12 +957,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-05-03</t>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-05-03</t>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,34 +981,28 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Carl A Andersson</t>
+          <t>Jonas Sjöblom</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Carl A Andersson</t>
+          <t>Jonas Sjöblom</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124749055</v>
+        <v>124026250</v>
       </c>
       <c r="B5" t="n">
-        <v>95719</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97986</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1026,45 +1010,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>210</v>
+        <v>221946</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>utan kapsel</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sundbergen V om Älvsbacka, Vrm</t>
+          <t>Tjuvtjärnen, Tjuvtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>423653</v>
+        <v>423537</v>
       </c>
       <c r="R5" t="n">
-        <v>6621145</v>
+        <v>6621174</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1088,17 +1064,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-05-03</t>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Protonema (förgrodden) på en murken låga</t>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1107,19 +1088,18 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Carl A Andersson</t>
+          <t>Jonas Sjöblom</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Carl A Andersson, Jonas Sjöblom</t>
+          <t>Jonas Sjöblom</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 12633-2025 artfynd.xlsx
+++ b/artfynd/A 12633-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124749055</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -889,6 +899,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124749064</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -996,6 +1011,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124026065</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1103,8 +1123,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124026250</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>